--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueru/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D65B6D-F4E4-2548-9D31-5F6BA54AC78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8965333-1639-7742-84EC-4945F51E0F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10700" yWindow="2300" windowWidth="19540" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,12 @@
     <sheet name="Carbon_Applicability" sheetId="7" r:id="rId7"/>
     <sheet name="Emission_Factors" sheetId="8" r:id="rId8"/>
     <sheet name="Mode_Speeds" sheetId="9" r:id="rId9"/>
-    <sheet name="Node_Border" sheetId="10" r:id="rId10"/>
-    <sheet name="Transshipment" sheetId="11" r:id="rId11"/>
-    <sheet name="Waiting_Costs" sheetId="12" r:id="rId12"/>
-    <sheet name="Notes" sheetId="13" r:id="rId13"/>
-    <sheet name="Source_Notes" sheetId="14" r:id="rId14"/>
+    <sheet name="Carbon_Tax_Applicability" sheetId="15" r:id="rId10"/>
+    <sheet name="Node_Border" sheetId="10" r:id="rId11"/>
+    <sheet name="Transshipment" sheetId="11" r:id="rId12"/>
+    <sheet name="Waiting_Costs" sheetId="12" r:id="rId13"/>
+    <sheet name="Notes" sheetId="13" r:id="rId14"/>
+    <sheet name="Source_Notes" sheetId="14" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Batches!$A$1:$G$11</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6066" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="184">
   <si>
     <t>EnglishName</t>
   </si>
@@ -571,6 +572,33 @@
     <t>time</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Applies</t>
+  </si>
+  <si>
+    <t>CN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROAD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAIL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WATER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1639,6 +1667,119 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F567ED83-350D-484F-BA47-6AEF008E7B02}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -2867,7 +3008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -4585,7 +4726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -4641,7 +4782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -4720,7 +4861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -37137,7 +37278,7 @@
         <v>72</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
         <v>122</v>
